--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45904</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>44642</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>44834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45988</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44840</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>44579</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44711</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>45873</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>44841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>44840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45642</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>46155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>46078</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46171</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>44574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>46030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>46160</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44515</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44705</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45905</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45224</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45044</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>44726</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45904</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>45215</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45531</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45957</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45911</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44545</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45224</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>44874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>44579</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44664</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44495</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>44475</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>44641</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44641</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44708</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>44531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>44763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>44519</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44524</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>44830</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44872</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44537</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>44706</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44615</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44505</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44711</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44496</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44788</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44980</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>44880</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44838</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45280</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44579</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45091</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45057</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>45182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>44991</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>45425</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>45288</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>45288</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>45392</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44880</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44992</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45007</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>44931</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45181</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>45201</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>44488</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>44496</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>44760</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>44834</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>45730</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44987</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45321</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>45288</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44872</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44676</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44596</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>44931</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>44826</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>44582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>45075</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45609</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>45434</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44834</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44540</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>45646</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44830</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>45384</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45253</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45056</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>44540</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44901</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44992</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45726</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45177</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>44616</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44571</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>44882</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44936</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45628</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45894</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45628</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>45628</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>46139</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45896</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>45071</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>44659</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>44644</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45072</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45525</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45204</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45006</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45288</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45146</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45131</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>46008</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45422</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45041</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44963</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45692</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45551</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44936</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44979</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45189</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44481</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44987</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45209</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45965</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45973</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45979</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45219</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45226</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45209</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>45525</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>45986</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45986</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45061</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44518</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>44525</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>44496</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>46077</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>44581</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44928</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>45226</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>44671</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45077</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>46167</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>46167</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45511</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>45898</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>45177</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46009</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45898</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>45044</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45044</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45237</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>46031</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>46030</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>46031</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>46030</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>46034</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45219</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>46034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>46035</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>46034</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>46034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>46035</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>46034</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>46171</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>46171</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>46171</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>46034</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>46034</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>46034</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>46035</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>46034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>46037</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>46036</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>46036</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>46036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>46036</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>46036</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>44579</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>46041</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46041</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>46174</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45980</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>46044</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>46044</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>44834</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>46035</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>44953</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>44846</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44998</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>46043</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45235</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44998</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>44987</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46073</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46075</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>46078</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45014</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44459</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45152</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>46087</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46188</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>44901</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>46188</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45957</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46195</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>46195</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44571</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44617</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45121</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45265</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44900</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45288</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44953</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>45051</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45733</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>46129</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>45204</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>46129</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>46129</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>46129</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>44496</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45684</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>44699</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>44831</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>44831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>44617</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>44980</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44931</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>45248</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44881</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44894</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45128</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45089</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>46212</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>44713</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45189</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>46217</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45016</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45058</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45681</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45681</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44613</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>46255</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>44827</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45401</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>46255</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45817</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>46272</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>46278</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>46278</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45001</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>44805</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45629</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45799</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45743</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45831</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45799</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45681</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45838</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45854</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45491</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45882</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>45235</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45226</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>45995</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>46027</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE319"/>
+  <dimension ref="A1:AE318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45904</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>44642</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>44834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45988</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44840</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>44579</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44711</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49759-2025</t>
+          <t>A 36799-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45939</v>
+        <v>45873</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -2562,387 +2562,387 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Blomkålssvamp
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 36799-2025 artfynd.xlsx", "A 36799-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 36799-2025 karta.png", "A 36799-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 36799-2025 georefererad karta.tif", "A 36799-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 36799-2025 FSC-klagomål.docx", "A 36799-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 36799-2025 FSC-klagomål mail.docx", "A 36799-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 36799-2025 tillsynsbegäran.docx", "A 36799-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 36799-2025 tillsynsbegäran mail.docx", "A 36799-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 49759-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>STRÄNGNÄS</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>4</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kandelabersvamp
 Guldlockmossa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 49759-2025 artfynd.xlsx", "A 49759-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 49759-2025 karta.png", "A 49759-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 49759-2025 georefererad karta.tif", "A 49759-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 49759-2025 FSC-klagomål.docx", "A 49759-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 49759-2025 FSC-klagomål mail.docx", "A 49759-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 49759-2025 tillsynsbegäran.docx", "A 49759-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 49759-2025 tillsynsbegäran mail.docx", "A 49759-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 24688-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>46171</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>STRÄNGNÄS</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>STRÄNGNÄS</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>5.1</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Blekticka
 Svartöra
 Ormbär</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 24688-2026 artfynd.xlsx", "A 24688-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 24688-2026 karta.png", "A 24688-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 24688-2026 georefererad karta.tif", "A 24688-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 24688-2026 FSC-klagomål.docx", "A 24688-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 24688-2026 FSC-klagomål mail.docx", "A 24688-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 24688-2026 tillsynsbegäran.docx", "A 24688-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 24688-2026 tillsynsbegäran mail.docx", "A 24688-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 52999-2025</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>45957</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>STRÄNGNÄS</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>STRÄNGNÄS</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>5.3</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grönpyrola
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 52999-2025 artfynd.xlsx", "A 52999-2025")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 52999-2025 karta.png", "A 52999-2025")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 52999-2025 georefererad karta.tif", "A 52999-2025")</f>
         <v/>
       </c>
-      <c r="Z20">
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/knärot/A 52999-2025 karta knärot.png", "A 52999-2025")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 52999-2025 FSC-klagomål.docx", "A 52999-2025")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 52999-2025 FSC-klagomål mail.docx", "A 52999-2025")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 52999-2025 tillsynsbegäran.docx", "A 52999-2025")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 52999-2025 tillsynsbegäran mail.docx", "A 52999-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 36799-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45873</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>STRÄNGNÄS</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Blomkålssvamp
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 36799-2025 artfynd.xlsx", "A 36799-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 36799-2025 karta.png", "A 36799-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 36799-2025 georefererad karta.tif", "A 36799-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 36799-2025 FSC-klagomål.docx", "A 36799-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 36799-2025 FSC-klagomål mail.docx", "A 36799-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 36799-2025 tillsynsbegäran.docx", "A 36799-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 36799-2025 tillsynsbegäran mail.docx", "A 36799-2025")</f>
         <v/>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
         <v>44841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>44840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45642</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>46155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>46078</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 40560-2025</t>
+          <t>A 24683-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3507,14 +3507,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45896</v>
+        <v>46171</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,22 +3527,22 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12.6</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -3560,153 +3560,153 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Gräshoppsångare
+Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 24683-2026 artfynd.xlsx", "A 24683-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 24683-2026 karta.png", "A 24683-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 24683-2026 georefererad karta.tif", "A 24683-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 24683-2026 FSC-klagomål.docx", "A 24683-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 24683-2026 FSC-klagomål mail.docx", "A 24683-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 24683-2026 tillsynsbegäran.docx", "A 24683-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 24683-2026 tillsynsbegäran mail.docx", "A 24683-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/fåglar/A 24683-2026 prioriterade fågelarter.docx", "A 24683-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 40560-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45896</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>STRÄNGNÄS</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
         <v>2</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Ask
 Åkergroda</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 40560-2025 artfynd.xlsx", "A 40560-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 40560-2025 karta.png", "A 40560-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 40560-2025 georefererad karta.tif", "A 40560-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 40560-2025 FSC-klagomål.docx", "A 40560-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 40560-2025 FSC-klagomål mail.docx", "A 40560-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 40560-2025 tillsynsbegäran.docx", "A 40560-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 40560-2025 tillsynsbegäran mail.docx", "A 40560-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 24683-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>STRÄNGNÄS</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Gräshoppsångare
-Enkelbeckasin</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 24683-2026 artfynd.xlsx", "A 24683-2026")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 24683-2026 karta.png", "A 24683-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 24683-2026 georefererad karta.tif", "A 24683-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 24683-2026 FSC-klagomål.docx", "A 24683-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 24683-2026 FSC-klagomål mail.docx", "A 24683-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 24683-2026 tillsynsbegäran.docx", "A 24683-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 24683-2026 tillsynsbegäran mail.docx", "A 24683-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/fåglar/A 24683-2026 prioriterade fågelarter.docx", "A 24683-2026")</f>
         <v/>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>44574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>46030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>46160</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44515</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44705</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45905</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45224</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18879-2023</t>
+          <t>A 42345-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4814,14 +4814,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45044</v>
+        <v>45904</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4834,23 +4834,23 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
@@ -4858,10 +4858,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4874,42 +4874,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 18879-2023 artfynd.xlsx", "A 18879-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 42345-2025 artfynd.xlsx", "A 42345-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 18879-2023 karta.png", "A 18879-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 42345-2025 karta.png", "A 42345-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 18879-2023 georefererad karta.tif", "A 18879-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 42345-2025 georefererad karta.tif", "A 42345-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 18879-2023 FSC-klagomål.docx", "A 18879-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 42345-2025 FSC-klagomål.docx", "A 42345-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 18879-2023 FSC-klagomål mail.docx", "A 18879-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 42345-2025 FSC-klagomål mail.docx", "A 42345-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 18879-2023 tillsynsbegäran.docx", "A 18879-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 42345-2025 tillsynsbegäran.docx", "A 42345-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 18879-2023 tillsynsbegäran mail.docx", "A 18879-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 42345-2025 tillsynsbegäran mail.docx", "A 42345-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24454-2022</t>
+          <t>A 18879-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4923,10 +4923,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44726</v>
+        <v>45044</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>12.5</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4975,50 +4975,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 24454-2022 artfynd.xlsx", "A 24454-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 18879-2023 artfynd.xlsx", "A 18879-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 24454-2022 karta.png", "A 24454-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 18879-2023 karta.png", "A 18879-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 24454-2022 georefererad karta.tif", "A 24454-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 18879-2023 georefererad karta.tif", "A 18879-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 24454-2022 FSC-klagomål.docx", "A 24454-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 18879-2023 FSC-klagomål.docx", "A 18879-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 24454-2022 FSC-klagomål mail.docx", "A 24454-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 18879-2023 FSC-klagomål mail.docx", "A 18879-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 24454-2022 tillsynsbegäran.docx", "A 24454-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 18879-2023 tillsynsbegäran.docx", "A 18879-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 24454-2022 tillsynsbegäran mail.docx", "A 24454-2022")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/fåglar/A 24454-2022 prioriterade fågelarter.docx", "A 24454-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 18879-2023 tillsynsbegäran mail.docx", "A 18879-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42345-2025</t>
+          <t>A 24454-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5028,14 +5024,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45904</v>
+        <v>44726</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5048,10 +5044,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -5063,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5072,10 +5068,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5084,46 +5080,50 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 42345-2025 artfynd.xlsx", "A 42345-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 24454-2022 artfynd.xlsx", "A 24454-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 42345-2025 karta.png", "A 42345-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 24454-2022 karta.png", "A 24454-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 42345-2025 georefererad karta.tif", "A 42345-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 24454-2022 georefererad karta.tif", "A 24454-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 42345-2025 FSC-klagomål.docx", "A 42345-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 24454-2022 FSC-klagomål.docx", "A 24454-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 42345-2025 FSC-klagomål mail.docx", "A 42345-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 24454-2022 FSC-klagomål mail.docx", "A 24454-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 42345-2025 tillsynsbegäran.docx", "A 42345-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 24454-2022 tillsynsbegäran.docx", "A 24454-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 42345-2025 tillsynsbegäran mail.docx", "A 42345-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 24454-2022 tillsynsbegäran mail.docx", "A 24454-2022")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/fåglar/A 24454-2022 prioriterade fågelarter.docx", "A 24454-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41511-2022</t>
+          <t>A 43391-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44827</v>
+        <v>45911</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5152,16 +5152,11 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -5191,49 +5186,53 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 41511-2022 artfynd.xlsx", "A 41511-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 43391-2025 artfynd.xlsx", "A 43391-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 41511-2022 karta.png", "A 41511-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 43391-2025 karta.png", "A 43391-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 41511-2022 georefererad karta.tif", "A 41511-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 43391-2025 georefererad karta.tif", "A 43391-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 41511-2022 FSC-klagomål.docx", "A 41511-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 43391-2025 FSC-klagomål.docx", "A 43391-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 41511-2022 FSC-klagomål mail.docx", "A 41511-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 43391-2025 FSC-klagomål mail.docx", "A 43391-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 41511-2022 tillsynsbegäran.docx", "A 41511-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 43391-2025 tillsynsbegäran.docx", "A 43391-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 41511-2022 tillsynsbegäran mail.docx", "A 41511-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 43391-2025 tillsynsbegäran mail.docx", "A 43391-2025")</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/fåglar/A 43391-2025 prioriterade fågelarter.docx", "A 43391-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50010-2023</t>
+          <t>A 41511-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5243,14 +5242,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45215</v>
+        <v>44827</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5264,21 +5263,21 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5292,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5301,49 +5300,49 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 50010-2023 artfynd.xlsx", "A 50010-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 41511-2022 artfynd.xlsx", "A 41511-2022")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 50010-2023 karta.png", "A 50010-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 41511-2022 karta.png", "A 41511-2022")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 50010-2023 georefererad karta.tif", "A 50010-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 41511-2022 georefererad karta.tif", "A 41511-2022")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 50010-2023 FSC-klagomål.docx", "A 50010-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 41511-2022 FSC-klagomål.docx", "A 41511-2022")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 50010-2023 FSC-klagomål mail.docx", "A 50010-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 41511-2022 FSC-klagomål mail.docx", "A 41511-2022")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 50010-2023 tillsynsbegäran.docx", "A 50010-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 41511-2022 tillsynsbegäran.docx", "A 41511-2022")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 50010-2023 tillsynsbegäran mail.docx", "A 50010-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 41511-2022 tillsynsbegäran mail.docx", "A 41511-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35360-2024</t>
+          <t>A 52997-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5357,10 +5356,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45531</v>
+        <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5372,26 +5371,21 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>1</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
@@ -5402,10 +5396,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5418,42 +5412,46 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 35360-2024 artfynd.xlsx", "A 35360-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 52997-2025 artfynd.xlsx", "A 52997-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 35360-2024 karta.png", "A 35360-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 52997-2025 karta.png", "A 52997-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 35360-2024 georefererad karta.tif", "A 35360-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 52997-2025 georefererad karta.tif", "A 52997-2025")</f>
+        <v/>
+      </c>
+      <c r="Z44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/knärot/A 52997-2025 karta knärot.png", "A 52997-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 35360-2024 FSC-klagomål.docx", "A 35360-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 52997-2025 FSC-klagomål.docx", "A 52997-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 35360-2024 FSC-klagomål mail.docx", "A 35360-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 52997-2025 FSC-klagomål mail.docx", "A 52997-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 35360-2024 tillsynsbegäran.docx", "A 35360-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 52997-2025 tillsynsbegäran.docx", "A 52997-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 35360-2024 tillsynsbegäran mail.docx", "A 35360-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 52997-2025 tillsynsbegäran mail.docx", "A 52997-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 52997-2025</t>
+          <t>A 50010-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5463,14 +5461,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45957</v>
+        <v>45215</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5482,8 +5480,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5495,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5507,10 +5510,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5523,46 +5526,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 52997-2025 artfynd.xlsx", "A 52997-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 50010-2023 artfynd.xlsx", "A 50010-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 52997-2025 karta.png", "A 52997-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 50010-2023 karta.png", "A 50010-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 52997-2025 georefererad karta.tif", "A 52997-2025")</f>
-        <v/>
-      </c>
-      <c r="Z45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/knärot/A 52997-2025 karta knärot.png", "A 52997-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 50010-2023 georefererad karta.tif", "A 50010-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 52997-2025 FSC-klagomål.docx", "A 52997-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 50010-2023 FSC-klagomål.docx", "A 50010-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 52997-2025 FSC-klagomål mail.docx", "A 52997-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 50010-2023 FSC-klagomål mail.docx", "A 50010-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 52997-2025 tillsynsbegäran.docx", "A 52997-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 50010-2023 tillsynsbegäran.docx", "A 50010-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 52997-2025 tillsynsbegäran mail.docx", "A 52997-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 50010-2023 tillsynsbegäran mail.docx", "A 50010-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43391-2025</t>
+          <t>A 35360-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5576,10 +5575,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45911</v>
+        <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5591,17 +5590,22 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5616,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5632,39 +5636,35 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 43391-2025 artfynd.xlsx", "A 43391-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/artfynd/A 35360-2024 artfynd.xlsx", "A 35360-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 43391-2025 karta.png", "A 43391-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor/A 35360-2024 karta.png", "A 35360-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 43391-2025 georefererad karta.tif", "A 43391-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/kartor_geotiff/A 35360-2024 georefererad karta.tif", "A 35360-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 43391-2025 FSC-klagomål.docx", "A 43391-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomål/A 35360-2024 FSC-klagomål.docx", "A 35360-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 43391-2025 FSC-klagomål mail.docx", "A 43391-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/klagomålsmail/A 35360-2024 FSC-klagomål mail.docx", "A 35360-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 43391-2025 tillsynsbegäran.docx", "A 43391-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsyn/A 35360-2024 tillsynsbegäran.docx", "A 35360-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 43391-2025 tillsynsbegäran mail.docx", "A 43391-2025")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0486/fåglar/A 43391-2025 prioriterade fågelarter.docx", "A 43391-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0486/tillsynsmail/A 35360-2024 tillsynsbegäran mail.docx", "A 35360-2024")</f>
         <v/>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
         <v>44545</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45224</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>44874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14024-2022</t>
+          <t>A 36853-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44650</v>
+        <v>44805</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 36853-2022</t>
+          <t>A 14024-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44805</v>
+        <v>44650</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
         <v>44579</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44664</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44495</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>44475</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>44641</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44641</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44708</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>44531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>44763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>44519</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22069-2022</t>
+          <t>A 67639-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7511,14 +7511,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44711</v>
+        <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7574,7 +7574,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 67639-2021</t>
+          <t>A 22069-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7584,14 +7584,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44524</v>
+        <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7664,7 +7664,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>44830</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44872</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44537</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>44706</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44615</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44505</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44711</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44496</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44788</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44980</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 53897-2022</t>
+          <t>A 65160-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8839,10 +8839,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44880</v>
+        <v>45288</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8898,7 +8898,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59060-2022</t>
+          <t>A 65163-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44904</v>
+        <v>45288</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8971,7 +8971,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 43946-2022</t>
+          <t>A 13807-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44838</v>
+        <v>45007</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9000,8 +9000,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9044,7 +9049,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 64355-2023</t>
+          <t>A 53897-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9058,10 +9063,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45280</v>
+        <v>44880</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9074,7 +9079,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9117,7 +9122,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2468-2022</t>
+          <t>A 64355-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9131,10 +9136,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44579</v>
+        <v>45280</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9146,13 +9151,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9195,7 +9195,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26282-2023</t>
+          <t>A 59060-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45091</v>
+        <v>44904</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9268,7 +9268,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21126-2023</t>
+          <t>A 43946-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9282,10 +9282,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45057</v>
+        <v>44838</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9341,7 +9341,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42806-2023</t>
+          <t>A 2468-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45182</v>
+        <v>44579</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9370,8 +9370,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9414,7 +9419,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 10867-2023</t>
+          <t>A 26282-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9428,10 +9433,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44991</v>
+        <v>45091</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9444,7 +9449,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9487,7 +9492,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18508-2024</t>
+          <t>A 10867-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9501,10 +9506,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45425</v>
+        <v>44991</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9517,7 +9522,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9560,7 +9565,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 65160-2023</t>
+          <t>A 42806-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9574,10 +9579,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45288</v>
+        <v>45182</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9590,7 +9595,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9633,7 +9638,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 65163-2023</t>
+          <t>A 21126-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9647,10 +9652,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45288</v>
+        <v>45057</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9663,7 +9668,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9706,7 +9711,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 14034-2024</t>
+          <t>A 18508-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9720,10 +9725,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45392</v>
+        <v>45425</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9736,7 +9741,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9779,7 +9784,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 53904-2022</t>
+          <t>A 11243-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9789,14 +9794,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44880</v>
+        <v>44992</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9809,7 +9814,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9852,7 +9857,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 11243-2023</t>
+          <t>A 14034-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9862,14 +9867,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44992</v>
+        <v>45392</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9882,7 +9887,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9925,7 +9930,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13807-2023</t>
+          <t>A 53904-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9939,10 +9944,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45007</v>
+        <v>44880</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9954,13 +9959,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>44931</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45181</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>45201</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>44488</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>44496</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 30375-2022</t>
+          <t>A 43386-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44760</v>
+        <v>44834</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10514,7 +10514,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 43386-2022</t>
+          <t>A 30375-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44834</v>
+        <v>44760</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10604,7 +10604,7 @@
         <v>45730</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44987</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45321</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 65161-2023</t>
+          <t>A 51763-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10820,10 +10820,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45288</v>
+        <v>44872</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10879,7 +10879,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 51763-2022</t>
+          <t>A 65161-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10893,10 +10893,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44872</v>
+        <v>45288</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 17066-2022</t>
+          <t>A 5805-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44676</v>
+        <v>44596</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11098,7 +11098,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 5805-2022</t>
+          <t>A 17066-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11112,10 +11112,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44596</v>
+        <v>44676</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11188,7 +11188,7 @@
         <v>44931</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>44826</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>44582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 23225-2023</t>
+          <t>A 12792-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11477,10 +11477,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45075</v>
+        <v>45384</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>7.1</v>
+        <v>19.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11536,7 +11536,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 52452-2024</t>
+          <t>A 59304-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11546,14 +11546,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45609</v>
+        <v>45253</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11609,7 +11609,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 20181-2024</t>
+          <t>A 43669-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11619,14 +11619,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45434</v>
+        <v>44834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11682,7 +11682,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 43669-2022</t>
+          <t>A 42117-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11696,10 +11696,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44834</v>
+        <v>44830</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11711,8 +11711,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11755,7 +11760,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 71414-2021</t>
+          <t>A 60747-2021</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11769,10 +11774,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44540</v>
+        <v>44496</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11785,7 +11790,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11828,7 +11833,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61567-2024</t>
+          <t>A 23225-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11838,14 +11843,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45646</v>
+        <v>45075</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11858,7 +11863,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11901,7 +11906,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 42117-2022</t>
+          <t>A 52452-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11911,14 +11916,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44830</v>
+        <v>45609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11928,11 +11933,6 @@
       <c r="G131" t="inlineStr">
         <is>
           <t>STRÄNGNÄS</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -11979,7 +11979,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 60747-2021</t>
+          <t>A 20181-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11989,14 +11989,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44496</v>
+        <v>45434</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12052,7 +12052,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 12792-2024</t>
+          <t>A 71414-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12066,10 +12066,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45384</v>
+        <v>44540</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>19.1</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12125,7 +12125,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 59304-2023</t>
+          <t>A 61567-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12135,14 +12135,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45253</v>
+        <v>45646</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12198,7 +12198,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 21015-2023</t>
+          <t>A 1117-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12212,10 +12212,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45056</v>
+        <v>44571</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12271,7 +12271,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 71391-2021</t>
+          <t>A 38198-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12285,10 +12285,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44540</v>
+        <v>45882</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 58238-2022</t>
+          <t>A 21015-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12358,10 +12358,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44901</v>
+        <v>45056</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12417,7 +12417,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 11690-2023</t>
+          <t>A 40112-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12431,10 +12431,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44992</v>
+        <v>45894</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12490,7 +12490,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11281-2025</t>
+          <t>A 56984-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12504,10 +12504,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45726</v>
+        <v>45628</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12563,7 +12563,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 42777-2023</t>
+          <t>A 71391-2021</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12577,10 +12577,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45177</v>
+        <v>44540</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12592,13 +12592,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12641,7 +12636,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33342-2023</t>
+          <t>A 58238-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12655,10 +12650,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45128</v>
+        <v>44901</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12671,7 +12666,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12714,7 +12709,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9511-2022</t>
+          <t>A 56989-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12728,10 +12723,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44616</v>
+        <v>45628</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12744,7 +12739,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12787,7 +12782,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1117-2022</t>
+          <t>A 11690-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12801,10 +12796,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44571</v>
+        <v>44992</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12817,7 +12812,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12860,7 +12855,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 54383-2022</t>
+          <t>A 11281-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12874,10 +12869,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44882</v>
+        <v>45726</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12890,7 +12885,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12933,7 +12928,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1305-2023</t>
+          <t>A 56988-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12947,10 +12942,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44936</v>
+        <v>45628</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12963,7 +12958,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13006,7 +13001,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 56984-2024</t>
+          <t>A 42777-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13020,10 +13015,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45628</v>
+        <v>45177</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13035,8 +13030,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13079,7 +13079,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 40112-2025</t>
+          <t>A 20187-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45894</v>
+        <v>46139</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13108,8 +13108,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13152,7 +13157,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56989-2024</t>
+          <t>A 40605-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13166,10 +13171,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45628</v>
+        <v>45896</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13182,7 +13187,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13225,7 +13230,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 56988-2024</t>
+          <t>A 33342-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13239,10 +13244,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45628</v>
+        <v>45128</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13255,7 +13260,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13298,7 +13303,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 20187-2026</t>
+          <t>A 9511-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13312,10 +13317,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46139</v>
+        <v>44616</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13327,13 +13332,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13376,7 +13376,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 40605-2025</t>
+          <t>A 54383-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13390,10 +13390,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45896</v>
+        <v>44882</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13449,7 +13449,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22522-2023</t>
+          <t>A 1305-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13463,10 +13463,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45071</v>
+        <v>44936</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13522,7 +13522,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 15397-2022</t>
+          <t>A 22522-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13536,10 +13536,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44659</v>
+        <v>45071</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13595,7 +13595,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 13259-2022</t>
+          <t>A 62746-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13609,10 +13609,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44644</v>
+        <v>46008</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13668,7 +13668,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 3118-2023</t>
+          <t>A 15397-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44946</v>
+        <v>44659</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 23001-2023</t>
+          <t>A 13259-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13755,10 +13755,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45072</v>
+        <v>44644</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 34391-2024</t>
+          <t>A 3118-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13828,10 +13828,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45525</v>
+        <v>44946</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13887,7 +13887,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 48875-2023</t>
+          <t>A 23001-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13901,10 +13901,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45204</v>
+        <v>45072</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13960,7 +13960,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13613-2023</t>
+          <t>A 34391-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13974,10 +13974,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45006</v>
+        <v>45525</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14033,7 +14033,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 65153-2023</t>
+          <t>A 48875-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14047,10 +14047,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45288</v>
+        <v>45204</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14106,7 +14106,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 35495-2023</t>
+          <t>A 13613-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14120,10 +14120,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45146</v>
+        <v>45006</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14179,7 +14179,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 34364-2023</t>
+          <t>A 65153-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45131</v>
+        <v>45288</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14252,7 +14252,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 62746-2025</t>
+          <t>A 10543-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46008</v>
+        <v>46077</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14281,8 +14281,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14325,7 +14330,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 18358-2024</t>
+          <t>A 35495-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14339,10 +14344,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45422</v>
+        <v>45146</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14355,7 +14360,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14398,7 +14403,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 18242-2023</t>
+          <t>A 34364-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14412,10 +14417,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45041</v>
+        <v>45131</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14427,13 +14432,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14476,7 +14476,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 5849-2023</t>
+          <t>A 54451-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14490,10 +14490,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44963</v>
+        <v>45965</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14549,7 +14549,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 3121-2023</t>
+          <t>A 23961-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14563,10 +14563,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44946</v>
+        <v>46167</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14622,7 +14622,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5458-2025</t>
+          <t>A 56124-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14632,14 +14632,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45692</v>
+        <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 39448-2024</t>
+          <t>A 57150-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45551</v>
+        <v>45979</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.2</v>
+        <v>13.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14768,7 +14768,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 1256-2023</t>
+          <t>A 23995-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14782,10 +14782,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44936</v>
+        <v>46167</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14841,7 +14841,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 9034-2023</t>
+          <t>A 58936-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14851,14 +14851,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44979</v>
+        <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14914,7 +14914,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 44479-2023</t>
+          <t>A 58935-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45189</v>
+        <v>45986</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14987,7 +14987,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 57048-2021</t>
+          <t>A 18358-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15001,10 +15001,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44481</v>
+        <v>45422</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15060,7 +15060,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 10352-2023</t>
+          <t>A 18242-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15074,10 +15074,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44987</v>
+        <v>45041</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15089,8 +15089,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15133,7 +15138,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 48886-2023</t>
+          <t>A 5849-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15147,10 +15152,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45209</v>
+        <v>44963</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15163,7 +15168,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15206,7 +15211,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 54451-2025</t>
+          <t>A 3121-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15220,10 +15225,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45965</v>
+        <v>44946</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15279,7 +15284,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 56124-2025</t>
+          <t>A 24680-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15289,14 +15294,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45973</v>
+        <v>46171</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15309,7 +15314,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15352,7 +15357,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 57150-2025</t>
+          <t>A 24691-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15366,10 +15371,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45979</v>
+        <v>46171</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15382,7 +15387,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>13.8</v>
+        <v>2.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15425,7 +15430,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 52773-2023</t>
+          <t>A 24694-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15439,10 +15444,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45219</v>
+        <v>46171</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15455,7 +15460,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15498,7 +15503,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 52840-2023</t>
+          <t>A 5458-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15512,10 +15517,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45226</v>
+        <v>45692</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15528,7 +15533,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15571,7 +15576,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 48823-2023</t>
+          <t>A 25077-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15581,14 +15586,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45209</v>
+        <v>46174</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15600,13 +15605,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15649,7 +15649,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34401-2024</t>
+          <t>A 39448-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15663,10 +15663,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45525</v>
+        <v>45551</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15722,7 +15722,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 58936-2025</t>
+          <t>A 1256-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15736,10 +15736,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45986</v>
+        <v>44936</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15795,7 +15795,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 58935-2025</t>
+          <t>A 9034-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15805,14 +15805,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45986</v>
+        <v>44979</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20938-2023</t>
+          <t>A 44479-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15882,10 +15882,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45061</v>
+        <v>45189</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15941,7 +15941,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 66296-2021</t>
+          <t>A 57048-2021</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15955,10 +15955,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44518</v>
+        <v>44481</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15970,13 +15970,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16019,7 +16014,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 67925-2021</t>
+          <t>A 41231-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16029,14 +16024,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44525</v>
+        <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16049,7 +16044,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16092,7 +16087,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 60764-2021</t>
+          <t>A 10352-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16106,10 +16101,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44496</v>
+        <v>44987</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16122,7 +16117,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16165,7 +16160,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 10543-2026</t>
+          <t>A 48886-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16179,10 +16174,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46077</v>
+        <v>45209</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16194,13 +16189,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16243,7 +16233,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 3037-2022</t>
+          <t>A 62988-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16257,10 +16247,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44581</v>
+        <v>46009</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16273,7 +16263,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16316,7 +16306,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 243-2023</t>
+          <t>A 41234-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16326,14 +16316,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44928</v>
+        <v>45898</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16346,7 +16336,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16389,7 +16379,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 52904-2023</t>
+          <t>A 52773-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16403,10 +16393,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45226</v>
+        <v>45219</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16419,7 +16409,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>9.9</v>
+        <v>1.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16462,7 +16452,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 16414-2022</t>
+          <t>A 52840-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16476,10 +16466,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44671</v>
+        <v>45226</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16491,13 +16481,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16540,7 +16525,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 23541-2023</t>
+          <t>A 1209-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16554,10 +16539,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45077</v>
+        <v>46031</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16570,7 +16555,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16613,7 +16598,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 23961-2026</t>
+          <t>A 48823-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16623,14 +16608,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46167</v>
+        <v>45209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16642,8 +16627,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16686,7 +16676,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 23995-2026</t>
+          <t>A 1108-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16700,10 +16690,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46167</v>
+        <v>46030</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16716,7 +16706,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16759,7 +16749,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 32079-2024</t>
+          <t>A 1313-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16773,10 +16763,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45511</v>
+        <v>46031</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16789,7 +16779,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16832,7 +16822,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 41231-2025</t>
+          <t>A 34401-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16842,14 +16832,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45898</v>
+        <v>45525</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16862,7 +16852,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16905,7 +16895,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 42750-2023</t>
+          <t>A 1018-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16919,10 +16909,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45177</v>
+        <v>46030</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16934,13 +16924,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16983,7 +16968,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 62988-2025</t>
+          <t>A 1680-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16997,10 +16982,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46009</v>
+        <v>46034</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17013,7 +16998,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17056,7 +17041,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 41234-2025</t>
+          <t>A 1718-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17066,14 +17051,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45898</v>
+        <v>46034</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17086,7 +17071,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17129,7 +17114,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 18860-2023</t>
+          <t>A 1892-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17143,10 +17128,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45044</v>
+        <v>46035</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17159,7 +17144,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17202,7 +17187,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 18865-2023</t>
+          <t>A 1511-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17216,10 +17201,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45044</v>
+        <v>46034</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17232,7 +17217,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17275,7 +17260,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 55054-2023</t>
+          <t>A 1553-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17289,10 +17274,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45237</v>
+        <v>46034</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17304,13 +17289,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17353,7 +17333,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 1209-2026</t>
+          <t>A 2007-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17367,10 +17347,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17383,7 +17363,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17426,7 +17406,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 1108-2026</t>
+          <t>A 1757-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17440,10 +17420,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17456,7 +17436,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17499,7 +17479,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 1313-2026</t>
+          <t>A 1624-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17513,10 +17493,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17529,7 +17509,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17572,7 +17552,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 1018-2026</t>
+          <t>A 1744-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17586,10 +17566,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17602,7 +17582,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17645,7 +17625,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 1680-2026</t>
+          <t>A 1660-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17662,7 +17642,7 @@
         <v>46034</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17675,7 +17655,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17718,7 +17698,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 52790-2023</t>
+          <t>A 1915-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17732,10 +17712,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45219</v>
+        <v>46035</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17748,7 +17728,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17791,7 +17771,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 1718-2026</t>
+          <t>A 1496-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17808,7 +17788,7 @@
         <v>46034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17821,7 +17801,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17864,7 +17844,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 1892-2026</t>
+          <t>A 2636-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17878,10 +17858,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17894,7 +17874,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17937,7 +17917,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 1511-2026</t>
+          <t>A 2368-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17951,10 +17931,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17967,7 +17947,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18010,7 +17990,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 1553-2026</t>
+          <t>A 2256-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18024,10 +18004,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18040,7 +18020,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18083,7 +18063,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 2007-2026</t>
+          <t>A 2328-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18097,10 +18077,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18113,7 +18093,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18156,7 +18136,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 1757-2026</t>
+          <t>A 2268-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18170,10 +18150,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18186,7 +18166,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18229,7 +18209,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 24680-2026</t>
+          <t>A 2302-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18243,10 +18223,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46171</v>
+        <v>46036</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18259,7 +18239,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18302,7 +18282,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 24691-2026</t>
+          <t>A 3127-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18316,10 +18296,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46171</v>
+        <v>46041</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18332,7 +18312,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18375,7 +18355,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 24694-2026</t>
+          <t>A 3207-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18389,10 +18369,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46171</v>
+        <v>46041</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18405,7 +18385,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18448,7 +18428,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 1624-2026</t>
+          <t>A 20938-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18462,10 +18442,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46034</v>
+        <v>45061</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18521,7 +18501,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 1744-2026</t>
+          <t>A 66296-2021</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18535,10 +18515,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46034</v>
+        <v>44518</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18550,8 +18530,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18594,7 +18579,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 1660-2026</t>
+          <t>A 27680-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18608,10 +18593,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46034</v>
+        <v>46188</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18624,7 +18609,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18667,7 +18652,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 1915-2026</t>
+          <t>A 57484-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18677,14 +18662,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46035</v>
+        <v>45980</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18697,7 +18682,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18740,7 +18725,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 1496-2026</t>
+          <t>A 27677-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18754,10 +18739,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46034</v>
+        <v>46188</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18770,7 +18755,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18813,7 +18798,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 2636-2026</t>
+          <t>A 67925-2021</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18827,10 +18812,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46037</v>
+        <v>44525</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18843,7 +18828,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18886,7 +18871,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 2368-2026</t>
+          <t>A 4151-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18900,10 +18885,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46036</v>
+        <v>46044</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18916,7 +18901,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18959,7 +18944,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 2256-2026</t>
+          <t>A 4112-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18973,10 +18958,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46036</v>
+        <v>46044</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18989,7 +18974,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19032,7 +19017,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 2328-2026</t>
+          <t>A 1977-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19046,10 +19031,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19062,7 +19047,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19105,7 +19090,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 2268-2026</t>
+          <t>A 60764-2021</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19119,10 +19104,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46036</v>
+        <v>44496</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19135,7 +19120,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19178,7 +19163,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 2302-2026</t>
+          <t>A 28102-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19188,14 +19173,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46036</v>
+        <v>46195</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19207,8 +19192,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19251,7 +19241,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 2497-2022</t>
+          <t>A 28108-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19261,14 +19251,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44579</v>
+        <v>46195</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19282,11 +19272,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19329,7 +19319,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 3127-2026</t>
+          <t>A 3037-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19343,10 +19333,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46041</v>
+        <v>44581</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19359,7 +19349,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19402,7 +19392,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 3207-2026</t>
+          <t>A 243-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19416,10 +19406,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46041</v>
+        <v>44928</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19432,7 +19422,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19475,7 +19465,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 25077-2026</t>
+          <t>A 52904-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19489,10 +19479,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46174</v>
+        <v>45226</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19505,7 +19495,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>5.4</v>
+        <v>9.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19548,7 +19538,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 57484-2025</t>
+          <t>A 3733-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19558,14 +19548,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45980</v>
+        <v>46043</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19578,7 +19568,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19621,7 +19611,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 4151-2026</t>
+          <t>A 16414-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19635,10 +19625,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46044</v>
+        <v>44671</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19650,8 +19640,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19694,7 +19689,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 4112-2026</t>
+          <t>A 23541-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19708,10 +19703,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46044</v>
+        <v>45077</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19724,7 +19719,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19767,7 +19762,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 43387-2022</t>
+          <t>A 32079-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19781,10 +19776,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44834</v>
+        <v>45511</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19797,7 +19792,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19840,7 +19835,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 1977-2026</t>
+          <t>A 42750-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19854,10 +19849,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46035</v>
+        <v>45177</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19869,8 +19864,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19913,7 +19913,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 4335-2023</t>
+          <t>A 9942-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19927,10 +19927,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44953</v>
+        <v>46073</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19942,13 +19942,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19991,7 +19986,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 45984-2022</t>
+          <t>A 10121-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20005,10 +20000,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44846</v>
+        <v>46075</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20021,7 +20016,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20064,7 +20059,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 12114-2023</t>
+          <t>A 10770-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20078,10 +20073,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44998</v>
+        <v>46078</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20094,7 +20089,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20137,7 +20132,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 3733-2026</t>
+          <t>A 18860-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20151,10 +20146,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46043</v>
+        <v>45044</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20167,7 +20162,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20210,7 +20205,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 54656-2023</t>
+          <t>A 18865-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20220,14 +20215,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45235</v>
+        <v>45044</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20240,7 +20235,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20283,7 +20278,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 12123-2023</t>
+          <t>A 12343-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20297,10 +20292,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44998</v>
+        <v>46087</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20313,7 +20308,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -20356,7 +20351,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 10346-2023</t>
+          <t>A 55054-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -20370,10 +20365,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44987</v>
+        <v>45237</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20385,8 +20380,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20429,7 +20429,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 9942-2026</t>
+          <t>A 52998-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20443,10 +20443,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46073</v>
+        <v>45957</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20502,7 +20502,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 10121-2026</t>
+          <t>A 52790-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20516,10 +20516,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46075</v>
+        <v>45219</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20575,7 +20575,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 10770-2026</t>
+          <t>A 2497-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20589,10 +20589,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46078</v>
+        <v>44579</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20604,8 +20604,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20648,7 +20653,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 14847-2023</t>
+          <t>A 43387-2022</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20662,10 +20667,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45014</v>
+        <v>44834</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20677,13 +20682,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20726,7 +20726,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 50296-2021</t>
+          <t>A 4335-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44459</v>
+        <v>44953</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20755,8 +20755,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20799,7 +20804,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 36469-2023</t>
+          <t>A 45984-2022</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20813,10 +20818,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45152</v>
+        <v>44846</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20828,13 +20833,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20877,7 +20877,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 12343-2026</t>
+          <t>A 12114-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20891,10 +20891,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46087</v>
+        <v>44998</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20950,7 +20950,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 27680-2026</t>
+          <t>A 54656-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20960,14 +20960,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46188</v>
+        <v>45235</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -21023,7 +21023,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 58241-2022</t>
+          <t>A 18971-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21037,10 +21037,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44901</v>
+        <v>46129</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21096,7 +21096,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 27677-2026</t>
+          <t>A 18965-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -21110,10 +21110,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46188</v>
+        <v>46129</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -21169,7 +21169,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 52998-2025</t>
+          <t>A 18904-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -21183,10 +21183,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45957</v>
+        <v>46129</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -21242,7 +21242,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 28102-2026</t>
+          <t>A 18961-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21252,14 +21252,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46195</v>
+        <v>46129</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21271,13 +21271,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I258" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -21320,7 +21315,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 28108-2026</t>
+          <t>A 12123-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -21330,14 +21325,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46195</v>
+        <v>44998</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21349,13 +21344,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -21398,7 +21388,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 1117-2022</t>
+          <t>A 4115-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21412,10 +21402,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>44571</v>
+        <v>45684</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21428,7 +21418,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21471,7 +21461,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 9625-2022</t>
+          <t>A 10346-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21485,10 +21475,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44617</v>
+        <v>44987</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21501,7 +21491,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21544,7 +21534,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 32552-2023</t>
+          <t>A 14847-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21558,10 +21548,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45121</v>
+        <v>45014</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21573,8 +21563,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I262" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21617,7 +21612,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 61656-2023</t>
+          <t>A 36469-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21631,10 +21626,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45265</v>
+        <v>45152</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21646,8 +21641,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I263" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21690,7 +21690,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 58022-2022</t>
+          <t>A 58241-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21704,10 +21704,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44900</v>
+        <v>44901</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21763,7 +21763,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 65151-2023</t>
+          <t>A 30753-2026</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21773,14 +21773,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45288</v>
+        <v>46212</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21792,8 +21792,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I265" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21836,7 +21841,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 4320-2023</t>
+          <t>A 1117-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21850,10 +21855,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44953</v>
+        <v>44571</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21865,13 +21870,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I266" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21914,7 +21914,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 20167-2023</t>
+          <t>A 31442-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21928,10 +21928,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45051</v>
+        <v>46217</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21987,7 +21987,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 12619-2025</t>
+          <t>A 9625-2022</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -22001,10 +22001,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45733</v>
+        <v>44617</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -22060,7 +22060,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 18971-2026</t>
+          <t>A 32552-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -22074,10 +22074,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46129</v>
+        <v>45121</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -22133,7 +22133,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 48827-2023</t>
+          <t>A 61656-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -22147,10 +22147,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45204</v>
+        <v>45265</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 18965-2026</t>
+          <t>A 34503-2026</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -22220,10 +22220,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>46129</v>
+        <v>46255</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22235,8 +22235,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I271" t="n">
-        <v>0.6</v>
+        <v>7.8</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -22279,7 +22284,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 18904-2026</t>
+          <t>A 58022-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -22293,10 +22298,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>46129</v>
+        <v>44900</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22309,7 +22314,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -22352,7 +22357,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 18961-2026</t>
+          <t>A 65151-2023</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -22366,10 +22371,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>46129</v>
+        <v>45288</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22382,7 +22387,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -22425,7 +22430,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 60749-2021</t>
+          <t>A 4320-2023</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -22439,10 +22444,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>44496</v>
+        <v>44953</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22452,6 +22457,11 @@
       <c r="G274" t="inlineStr">
         <is>
           <t>STRÄNGNÄS</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I274" t="n">
@@ -22498,7 +22508,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 4115-2025</t>
+          <t>A 20167-2023</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -22512,10 +22522,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45684</v>
+        <v>45051</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22528,7 +22538,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -22571,7 +22581,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 20506-2022</t>
+          <t>A 12619-2025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -22585,10 +22595,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>44699</v>
+        <v>45733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22601,7 +22611,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -22644,7 +22654,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 42476-2022</t>
+          <t>A 48827-2023</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -22658,10 +22668,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>44831</v>
+        <v>45204</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22674,7 +22684,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -22717,7 +22727,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 42503-2022</t>
+          <t>A 60749-2021</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -22731,10 +22741,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>44831</v>
+        <v>44496</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22747,7 +22757,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22790,7 +22800,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 9704-2022</t>
+          <t>A 34486-2026</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22804,10 +22814,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>44617</v>
+        <v>46255</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22819,8 +22829,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I279" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22863,7 +22878,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 9232-2023</t>
+          <t>A 36669-2026</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22873,14 +22888,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>44980</v>
+        <v>46272</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22893,7 +22908,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22936,7 +22951,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 866-2023</t>
+          <t>A 20506-2022</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22950,10 +22965,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>44931</v>
+        <v>44699</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22966,7 +22981,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -23009,7 +23024,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 58092-2023</t>
+          <t>A 42476-2022</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -23019,14 +23034,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45248</v>
+        <v>44831</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23039,7 +23054,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>28.5</v>
+        <v>5.5</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -23082,7 +23097,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 54598-2022</t>
+          <t>A 42503-2022</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -23096,10 +23111,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>44881</v>
+        <v>44831</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23112,7 +23127,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -23155,7 +23170,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 56914-2022</t>
+          <t>A 9704-2022</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -23169,10 +23184,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>44894</v>
+        <v>44617</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23185,7 +23200,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>13.2</v>
+        <v>1.7</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -23228,7 +23243,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>A 33343-2023</t>
+          <t>A 37681-2026</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -23242,10 +23257,10 @@
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>45128</v>
+        <v>46278</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23257,8 +23272,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I285" t="n">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -23301,7 +23321,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>A 25542-2023</t>
+          <t>A 37682-2026</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -23315,10 +23335,10 @@
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>45089</v>
+        <v>46278</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23328,6 +23348,11 @@
       <c r="G286" t="inlineStr">
         <is>
           <t>STRÄNGNÄS</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I286" t="n">
@@ -23374,7 +23399,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A 30753-2026</t>
+          <t>A 9232-2023</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -23384,14 +23409,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>46212</v>
+        <v>44980</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23403,13 +23428,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I287" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -23452,7 +23472,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A 22459-2022</t>
+          <t>A 866-2023</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -23466,10 +23486,10 @@
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>44713</v>
+        <v>44931</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23481,13 +23501,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I288" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -23530,7 +23545,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A 44618-2023</t>
+          <t>A 58092-2023</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -23540,14 +23555,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>45189</v>
+        <v>45248</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23560,7 +23575,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>4.5</v>
+        <v>28.5</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -23603,7 +23618,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>A 31442-2026</t>
+          <t>A 54598-2022</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -23617,10 +23632,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>46217</v>
+        <v>44881</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23633,7 +23648,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -23676,7 +23691,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>A 15193-2023</t>
+          <t>A 56914-2022</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -23690,10 +23705,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>45016</v>
+        <v>44894</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23706,7 +23721,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>7.6</v>
+        <v>13.2</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -23749,7 +23764,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A 20815-2023</t>
+          <t>A 33343-2023</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -23763,10 +23778,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>45058</v>
+        <v>45128</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23779,7 +23794,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23822,7 +23837,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A 3759-2025</t>
+          <t>A 25542-2023</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23836,10 +23851,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>45681</v>
+        <v>45089</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23852,7 +23867,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23895,7 +23910,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>A 3761-2025</t>
+          <t>A 22459-2022</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -23909,10 +23924,10 @@
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>45681</v>
+        <v>44713</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23924,8 +23939,13 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I294" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -23968,7 +23988,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A 8493-2022</t>
+          <t>A 44618-2023</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -23982,10 +24002,10 @@
         </is>
       </c>
       <c r="D295" s="1" t="n">
-        <v>44613</v>
+        <v>45189</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23998,7 +24018,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -24041,7 +24061,7 @@
     <row r="296" ht="15" customHeight="1">
       <c r="A296" t="inlineStr">
         <is>
-          <t>A 34503-2026</t>
+          <t>A 15193-2023</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -24055,10 +24075,10 @@
         </is>
       </c>
       <c r="D296" s="1" t="n">
-        <v>46255</v>
+        <v>45016</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24070,13 +24090,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I296" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -24119,7 +24134,7 @@
     <row r="297" ht="15" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
-          <t>A 41503-2022</t>
+          <t>A 20815-2023</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -24133,10 +24148,10 @@
         </is>
       </c>
       <c r="D297" s="1" t="n">
-        <v>44827</v>
+        <v>45058</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24149,7 +24164,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -24192,7 +24207,7 @@
     <row r="298" ht="15" customHeight="1">
       <c r="A298" t="inlineStr">
         <is>
-          <t>A 15572-2024</t>
+          <t>A 3759-2025</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -24206,10 +24221,10 @@
         </is>
       </c>
       <c r="D298" s="1" t="n">
-        <v>45401</v>
+        <v>45681</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24222,7 +24237,7 @@
         </is>
       </c>
       <c r="I298" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
@@ -24265,7 +24280,7 @@
     <row r="299" ht="15" customHeight="1">
       <c r="A299" t="inlineStr">
         <is>
-          <t>A 34486-2026</t>
+          <t>A 3761-2025</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -24279,10 +24294,10 @@
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>46255</v>
+        <v>45681</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24294,13 +24309,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I299" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
@@ -24343,7 +24353,7 @@
     <row r="300" ht="15" customHeight="1">
       <c r="A300" t="inlineStr">
         <is>
-          <t>A 28104-2025</t>
+          <t>A 8493-2022</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -24357,10 +24367,10 @@
         </is>
       </c>
       <c r="D300" s="1" t="n">
-        <v>45817</v>
+        <v>44613</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24373,7 +24383,7 @@
         </is>
       </c>
       <c r="I300" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -24416,7 +24426,7 @@
     <row r="301" ht="15" customHeight="1">
       <c r="A301" t="inlineStr">
         <is>
-          <t>A 36669-2026</t>
+          <t>A 41503-2022</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -24426,14 +24436,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D301" s="1" t="n">
-        <v>46272</v>
+        <v>44827</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24446,7 +24456,7 @@
         </is>
       </c>
       <c r="I301" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J301" t="n">
         <v>0</v>
@@ -24489,7 +24499,7 @@
     <row r="302" ht="15" customHeight="1">
       <c r="A302" t="inlineStr">
         <is>
-          <t>A 37681-2026</t>
+          <t>A 15572-2024</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -24503,10 +24513,10 @@
         </is>
       </c>
       <c r="D302" s="1" t="n">
-        <v>46278</v>
+        <v>45401</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24518,13 +24528,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I302" t="n">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J302" t="n">
         <v>0</v>
@@ -24567,7 +24572,7 @@
     <row r="303" ht="15" customHeight="1">
       <c r="A303" t="inlineStr">
         <is>
-          <t>A 37682-2026</t>
+          <t>A 28104-2025</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -24581,10 +24586,10 @@
         </is>
       </c>
       <c r="D303" s="1" t="n">
-        <v>46278</v>
+        <v>45817</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24596,13 +24601,8 @@
           <t>STRÄNGNÄS</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I303" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
@@ -24662,7 +24662,7 @@
         <v>45001</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>44805</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45629</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45799</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45743</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45831</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45799</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45681</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45838</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45854</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45491</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25453,24 +25453,24 @@
     <row r="315" ht="15" customHeight="1">
       <c r="A315" t="inlineStr">
         <is>
-          <t>A 38198-2025</t>
+          <t>S 3845-2023</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D315" s="1" t="n">
-        <v>45882</v>
+        <v>45235</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         </is>
       </c>
       <c r="I315" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
@@ -25526,7 +25526,7 @@
     <row r="316" ht="15" customHeight="1">
       <c r="A316" t="inlineStr">
         <is>
-          <t>S 3845-2023</t>
+          <t>S 3717-2023</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -25540,10 +25540,10 @@
         </is>
       </c>
       <c r="D316" s="1" t="n">
-        <v>45235</v>
+        <v>45226</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         </is>
       </c>
       <c r="I316" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J316" t="n">
         <v>0</v>
@@ -25599,7 +25599,7 @@
     <row r="317" ht="15" customHeight="1">
       <c r="A317" t="inlineStr">
         <is>
-          <t>S 3717-2023</t>
+          <t>S 3431-2025</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -25613,10 +25613,10 @@
         </is>
       </c>
       <c r="D317" s="1" t="n">
-        <v>45226</v>
+        <v>45995</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         </is>
       </c>
       <c r="I317" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -25669,10 +25669,10 @@
       </c>
       <c r="V317" s="2" t="inlineStr"/>
     </row>
-    <row r="318" ht="15" customHeight="1">
+    <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>S 3431-2025</t>
+          <t>S 41-2026</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -25686,10 +25686,10 @@
         </is>
       </c>
       <c r="D318" s="1" t="n">
-        <v>45995</v>
+        <v>46027</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         </is>
       </c>
       <c r="I318" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -25741,79 +25741,6 @@
         <v>0</v>
       </c>
       <c r="V318" s="2" t="inlineStr"/>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>S 41-2026</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D319" s="1" t="n">
-        <v>46027</v>
-      </c>
-      <c r="E319" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>STRÄNGNÄS</t>
-        </is>
-      </c>
-      <c r="I319" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J319" t="n">
-        <v>0</v>
-      </c>
-      <c r="K319" t="n">
-        <v>0</v>
-      </c>
-      <c r="L319" t="n">
-        <v>0</v>
-      </c>
-      <c r="M319" t="n">
-        <v>0</v>
-      </c>
-      <c r="N319" t="n">
-        <v>0</v>
-      </c>
-      <c r="O319" t="n">
-        <v>0</v>
-      </c>
-      <c r="P319" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
-      <c r="R319" t="n">
-        <v>0</v>
-      </c>
-      <c r="S319" t="n">
-        <v>0</v>
-      </c>
-      <c r="T319" t="n">
-        <v>0</v>
-      </c>
-      <c r="U319" t="n">
-        <v>0</v>
-      </c>
-      <c r="V319" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45904</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44642</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>44834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45988</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44840</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>44579</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44711</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45939</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46171</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45873</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45896</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>46155</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>46171</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>46160</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44515</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44705</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45215</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45224</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45957</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45904</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45905</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45911</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>44726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>44545</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>45044</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45224</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44805</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44650</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44579</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44664</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44495</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>44852</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44475</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>44641</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>44641</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>44708</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>44531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>44763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44519</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44799</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44830</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44872</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44706</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44537</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44615</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44505</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44711</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44496</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44788</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>45044</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45044</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44826</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45401</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45434</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>45384</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>45392</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>44831</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>44831</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45075</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>44931</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45219</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45226</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44904</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44881</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44581</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>46030</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45629</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46030</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>46031</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>46034</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44481</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>46034</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>46034</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>46031</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44928</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>46034</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>46034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>46034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>46034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>46034</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>46035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>46036</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>46035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>46036</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>46036</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>46036</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>46036</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>46035</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>46037</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>46041</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>45894</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>46041</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45980</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>46035</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45646</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44671</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>46043</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>45280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44616</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45692</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>46075</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>46073</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45146</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>46078</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44617</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>45730</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44936</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44659</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>46087</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45209</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>45209</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45957</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45235</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45551</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>44946</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44998</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44931</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44496</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44991</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45743</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45965</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44936</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>46129</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>46129</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46129</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>46129</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45979</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45057</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>45896</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45684</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45986</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45628</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44540</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44713</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45511</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45182</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45051</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>45898</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>46009</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44953</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45628</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>45007</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>46139</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45628</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45248</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44931</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45016</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>45831</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>46008</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45077</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45204</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>45204</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>45733</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>44496</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45321</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45838</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>46077</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45799</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45681</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45071</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44518</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44901</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45128</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45288</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>46167</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>46167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45121</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>44571</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45854</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45491</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>46171</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45152</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>46171</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>46171</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>46174</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44980</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45177</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45288</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45288</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45265</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45288</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44613</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>46188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>46188</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45071</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>46195</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>46195</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44579</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44579</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45882</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44676</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>44830</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>46212</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45177</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>46217</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46255</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45253</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45201</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45681</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45681</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45189</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45726</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45525</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>46255</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45219</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>46272</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45237</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44946</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44987</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>44827</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44496</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>46278</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>46278</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45128</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>44882</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44582</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45288</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>44834</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>44496</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44699</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44880</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45525</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>46288</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>44992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>44540</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44488</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>44998</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45189</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45072</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44617</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45425</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45006</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45056</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44760</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44894</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45041</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45422</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>44987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44963</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44834</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45014</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45089</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45061</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45131</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44872</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45058</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44525</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44644</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45181</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44987</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>44979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>44596</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44846</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>44953</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44880</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45817</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45226</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>44805</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45001</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45235</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45226</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45995</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>46027</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45904</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44642</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>44834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45988</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44840</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>44579</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44711</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45939</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46171</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45873</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45896</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>46155</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>46171</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>46160</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44515</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44705</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45215</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45224</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45957</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45904</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45905</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45911</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>44726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>44545</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>45044</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45224</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44805</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44650</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44579</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44664</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44495</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>44852</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44475</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>44641</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>44641</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>44708</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>44531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>44763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44519</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44799</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44830</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44872</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44706</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44537</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44615</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44505</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44711</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44496</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44788</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>45044</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45044</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44826</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45401</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45434</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>45384</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>45392</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>44831</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>44831</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45075</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>44931</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45219</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45226</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44904</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44881</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44581</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>46030</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45629</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46030</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>46031</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>46034</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44481</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>46034</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>46034</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>46031</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44928</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>46034</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>46034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>46034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>46034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>46034</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>46035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>46036</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>46035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>46036</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>46036</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>46036</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>46036</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>46035</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>46037</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>46041</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>45894</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>46041</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45980</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>46035</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45646</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44671</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>46043</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>45280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44616</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45692</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>46075</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>46073</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45146</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>46078</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44617</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>45730</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44936</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44659</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>46087</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45209</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>45209</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45957</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45235</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45551</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>44946</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44998</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44931</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44496</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44991</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45743</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45965</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44936</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>46129</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>46129</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46129</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>46129</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45979</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45057</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>45896</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45684</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45986</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45628</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44540</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44713</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45511</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45182</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45051</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>45898</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>46009</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44953</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45628</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>45007</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>46139</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45628</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45248</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44931</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45016</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>45831</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>46008</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45077</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45204</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>45204</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>45733</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>44496</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45321</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45838</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>46077</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45799</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45681</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45071</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44518</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44901</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45128</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45288</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>46167</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>46167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45121</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>44571</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45854</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45491</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>46171</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45152</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>46171</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>46171</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>46174</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44980</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45177</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45288</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45288</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45265</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45288</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44613</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>46188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>46188</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45071</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>46195</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>46195</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44579</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44579</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45882</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44676</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>44830</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>46212</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45177</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>46217</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46255</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45253</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45201</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45681</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45681</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45189</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45726</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45525</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>46255</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45219</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>46272</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45237</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44946</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44987</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>44827</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44496</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>46278</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>46278</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45128</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>44882</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44582</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45288</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>44834</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>44496</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44699</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44880</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45525</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>46288</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>44992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>44540</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44488</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>44998</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45189</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45072</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44617</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45425</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45006</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45056</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44760</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44894</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45041</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45422</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>44987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44963</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44834</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45014</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45089</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45061</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45131</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44872</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45058</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44525</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44644</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45181</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44987</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>44979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>44596</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44846</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>44953</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44880</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45817</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45226</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>44805</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45001</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45235</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45226</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45995</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>46027</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45904</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44642</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>44834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45988</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44840</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>44579</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44711</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45939</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46171</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>45642</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>45896</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>46155</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>46078</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>46171</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>44574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>46160</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44515</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44705</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45904</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44930</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45957</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45905</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45224</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45044</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44726</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44827</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45911</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45215</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44545</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45224</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44805</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44874</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44650</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44579</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44664</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44495</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44475</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>44641</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>44641</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>44708</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>44531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>44763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44519</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44830</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44872</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44537</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44706</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44615</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44505</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44711</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44496</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44788</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44980</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45288</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>45288</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45007</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45280</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>44904</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44838</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>44579</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45091</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45182</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>44991</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45057</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>44992</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44805</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45425</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45392</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44880</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>45898</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>46009</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44931</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45181</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44571</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45894</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44488</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>46031</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>44508</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>46030</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>46031</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45201</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>46034</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>46035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>46034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>46034</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>46035</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>46034</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>46034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>46034</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>46034</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>46035</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>46034</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>46037</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>46036</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>46036</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>46036</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46036</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>46036</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>46041</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>46041</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45980</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>46044</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>45629</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>46044</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>46035</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45799</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44760</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>44834</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45730</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>46043</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44987</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45321</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>46073</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45288</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>46075</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44872</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45071</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>46078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44676</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44931</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>44596</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>46087</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44826</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45957</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45743</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45075</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45965</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45609</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>45434</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45384</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45253</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44834</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44830</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44496</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45973</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45979</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44540</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45646</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45986</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45056</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>44540</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44901</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>46129</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>44992</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45726</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>46129</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>46129</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>45177</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>46129</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45128</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45831</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44616</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44882</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44936</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45684</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45799</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45681</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45838</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45071</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44659</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44644</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45854</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45072</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45628</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45525</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45628</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45628</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45204</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>46139</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45491</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45006</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45896</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>45288</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45146</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45131</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45422</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45041</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44963</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44946</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45692</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45551</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>46008</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>44936</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>44979</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45189</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>44481</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44987</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45209</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>46077</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45219</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45226</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>46167</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>46167</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45209</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45525</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>46171</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>46171</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>46171</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>46174</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45061</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44518</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45882</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44525</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44496</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44581</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44928</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45226</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>44671</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45077</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46188</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46188</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45511</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46195</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45177</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>46195</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45044</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45044</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45237</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45219</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44579</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>46212</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>46217</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44834</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44953</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>44846</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>44998</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45235</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44998</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44987</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46272</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45014</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>46278</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>46278</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45152</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>44901</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>44571</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44617</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45121</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45265</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>44900</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45288</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44953</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>46288</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45051</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>45733</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45204</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44496</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44699</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44831</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>46255</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>46255</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>44617</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44931</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45248</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44881</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44894</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45128</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45089</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44713</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45189</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45016</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45058</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>45681</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44613</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44827</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45401</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45817</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45001</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45235</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45226</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45995</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>46027</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>83</v>
       </c>
       <c r="T2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45904</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44642</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>44834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45988</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44840</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>44579</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44711</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45939</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46171</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>45642</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>45896</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>46155</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>46078</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>46171</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>44574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>46160</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44515</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44705</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45904</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44930</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45957</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45905</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45224</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45044</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44726</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44827</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45911</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45215</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44545</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45224</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44805</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44874</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44650</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44579</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44664</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44495</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44475</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>44641</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>44641</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>44708</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>44531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>44763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44519</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44830</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44872</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44537</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44706</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44615</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44505</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44711</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44496</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44788</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44980</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45288</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>45288</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45007</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45280</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>44904</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44838</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>44579</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45091</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45182</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>44991</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45057</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>44992</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44805</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45425</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45392</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44880</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>45898</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>46009</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44931</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45181</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44571</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45894</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44488</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>46031</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>44508</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>46030</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>46031</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45201</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>46034</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>46035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>46034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>46034</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>46035</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>46034</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>46034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>46034</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>46034</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>46035</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>46034</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>46037</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>46036</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>46036</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>46036</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46036</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>46036</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>46041</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>46041</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45980</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>46044</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>45629</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>46044</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>46035</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45799</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44760</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>44834</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45730</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>46043</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44987</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45321</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>46073</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45288</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>46075</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44872</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45071</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>46078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44676</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44931</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>44596</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>46087</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44826</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45957</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45743</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45075</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45965</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45609</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>45434</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45384</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45253</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44834</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44830</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44496</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45973</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45979</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44540</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45646</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45986</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45056</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>44540</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44901</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>46129</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>44992</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45726</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>46129</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>46129</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>45177</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>46129</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45128</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45831</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44616</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44882</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44936</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45684</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45799</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45681</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45838</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45071</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44659</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44644</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45854</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45072</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45628</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45525</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45628</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45628</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45204</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>46139</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45491</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45006</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45896</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>45288</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45146</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45131</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45422</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45041</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44963</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44946</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45692</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45551</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>46008</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>44936</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>44979</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45189</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>44481</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44987</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45209</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>46077</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45219</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45226</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>46167</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>46167</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45209</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45525</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>46171</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>46171</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>46171</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>46174</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45061</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44518</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45882</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44525</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44496</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44581</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44928</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45226</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>44671</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45077</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46188</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46188</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45511</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46195</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45177</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>46195</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45044</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45044</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45237</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45219</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44579</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>46212</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>46217</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44834</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44953</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>44846</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>44998</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45235</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44998</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44987</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46272</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45014</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>46278</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>46278</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45152</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>44901</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>44571</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44617</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45121</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45265</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>44900</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45288</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44953</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>46288</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45051</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>45733</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45204</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44496</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44699</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44831</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>46255</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>46255</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>44617</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44931</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45248</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44881</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44894</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45128</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45089</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44713</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45189</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45016</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45058</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>45681</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44613</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44827</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45401</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45817</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45001</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45235</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45226</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45995</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>46027</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45904</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44642</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>44834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45988</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44840</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>44579</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44530</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44711</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>45873</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46171</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44840</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44845</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>46155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>46171</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>46160</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44515</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44705</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45215</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45224</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45044</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45224</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44726</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45531</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>45904</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>44545</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45905</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>45957</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>45911</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44805</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44650</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44579</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44664</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44495</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44608</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44550</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44641</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>44641</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>44623</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44708</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>44873</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>44524</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44505</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44711</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44531</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44872</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44763</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44830</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44519</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44854</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44617</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44537</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44706</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44711</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45061</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45091</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>45131</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44617</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44496</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>44872</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44788</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45434</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45384</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>45077</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>45204</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>45204</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45044</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45044</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45392</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44496</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45058</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44525</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44644</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45321</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44831</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44831</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45071</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44518</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45075</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44901</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45128</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>44931</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45401</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>45219</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45288</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44826</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45226</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45121</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>44571</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>45181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>44980</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>44904</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44987</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44881</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>44900</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44834</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44979</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>44596</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44571</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>44846</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44953</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44581</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>45152</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>44936</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44508</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44980</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45894</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44481</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44928</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45177</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44880</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>45288</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45288</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45226</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45646</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>45265</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44671</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44613</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45280</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44616</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45071</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45692</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45146</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45609</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44579</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>44617</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45730</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45629</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44936</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>44659</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45799</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>44676</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45209</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45209</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45235</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>44830</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>45551</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44992</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>44946</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45743</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44998</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>44931</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44496</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>44991</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45831</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>44936</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45253</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45201</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45681</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45681</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45838</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45799</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45681</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45057</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45189</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45965</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45854</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45726</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45491</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45525</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>44540</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44713</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45511</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45182</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45051</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45219</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45237</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45979</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44987</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44827</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>44953</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45882</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>44496</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45007</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45128</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44882</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45986</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>44582</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45288</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44901</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45248</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44834</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>44931</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44838</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45016</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45986</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44496</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44699</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>44880</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>46129</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>46129</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>45525</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>46129</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>46129</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>44992</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>44540</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>44488</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>44998</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45898</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45189</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45896</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45684</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45072</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45628</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>46009</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44617</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45425</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45006</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>45056</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>44760</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44894</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>46030</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45041</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>46030</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45422</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>46031</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>46034</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>46034</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>46034</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>46031</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>46034</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>46034</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>46034</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>46034</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>46034</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>46034</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>46035</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>46036</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>46035</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>46036</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>46036</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>46036</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>46036</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>46035</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>46037</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>46041</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>46041</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45980</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>46044</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44987</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>46044</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>46035</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44963</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45628</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>44834</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45014</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>46139</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45628</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45089</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46043</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>46008</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>46075</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>46073</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>46078</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46087</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>46077</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>46167</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>46167</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>46171</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46171</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>46171</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>46174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>46188</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>46195</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>46195</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>46212</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>46217</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>46272</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>46278</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46278</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>46288</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>46255</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>46255</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45235</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45226</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45995</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>46027</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>44642</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>44834</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44641</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45988</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>44840</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>44579</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44711</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44530</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>44841</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>45642</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>46155</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>46078</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46171</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>45896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>44845</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>44574</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45310</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>46030</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>46160</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44515</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44930</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45905</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45224</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>45904</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>44726</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45215</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>45911</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44545</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45224</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44579</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44664</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44852</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44495</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44608</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44641</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44641</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44708</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44763</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44519</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44873</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44524</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44711</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44830</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44799</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44872</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44872</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44617</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44706</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44505</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44711</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44617</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44496</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44788</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44980</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45288</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>45288</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45007</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>44880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45280</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44838</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44579</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45091</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44991</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>45057</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>45425</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>45392</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44880</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>44931</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45181</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>44508</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>44488</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45201</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44760</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44834</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45730</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44987</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45321</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44872</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45288</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45071</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44676</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>44931</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44596</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44826</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44582</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45075</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>45609</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>45434</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>45384</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>44834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>45253</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>44830</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>44540</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>45646</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>45882</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>45056</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>45628</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>44540</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>44901</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44992</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45726</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>45628</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>45177</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>45128</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>45894</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>44616</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>45628</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>46139</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>44882</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>44936</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45896</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45071</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44659</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>46008</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>44644</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>45072</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>45525</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>45204</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>45006</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45288</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45146</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>45131</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45422</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>45041</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45965</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44963</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>44946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>46077</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>45973</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45979</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>45692</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>45551</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>44936</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>44979</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>46167</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45189</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45986</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44987</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45209</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>45986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>46167</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>45219</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45226</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>45209</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>46171</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>46171</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45525</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45898</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>46171</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>46009</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>46174</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45061</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>44518</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44525</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>44496</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>44581</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>46031</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>44928</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>46030</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45226</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>46031</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>46030</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>46034</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>46034</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>46035</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>46034</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>44671</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>46035</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45077</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>46034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>46034</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>46034</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>46034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>46035</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>46034</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>46037</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>46036</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>46036</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>46036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>46036</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>46041</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>46041</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45980</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>46044</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45511</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46044</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>46035</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45177</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>46043</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45044</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45044</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45237</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>46073</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>46188</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>46075</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>46078</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45219</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>46188</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44579</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>46087</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45957</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>46195</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>46195</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44834</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44953</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44846</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44998</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45235</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>44998</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>46129</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>44987</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>46129</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>46129</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>46129</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45014</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45684</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45152</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>44901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44571</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44617</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45121</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>46212</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>46217</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44900</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45288</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>44953</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45051</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>46272</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45733</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45204</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44496</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>46278</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>46278</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44699</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>44831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44831</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44617</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>44980</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>44931</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45248</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>44881</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>44894</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45128</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45089</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>46288</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>44713</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45016</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45058</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45681</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45681</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44613</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44827</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45401</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>46255</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45817</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>46255</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45001</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44805</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45629</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45799</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45743</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45831</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45799</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45838</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45854</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45491</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45235</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45226</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>45995</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>46027</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>44642</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>44834</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44641</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45988</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>44840</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>44579</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44711</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44530</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>44841</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>45642</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>46155</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>46078</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46171</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>45896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>44845</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>44574</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45310</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>46030</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>46160</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44515</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44930</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45905</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45224</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>45904</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>44726</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45215</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>45911</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44545</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45224</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44579</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44664</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44852</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44495</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44608</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44641</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44641</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44708</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44763</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44519</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44873</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44524</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44711</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44830</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44799</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44872</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44872</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44617</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44706</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44505</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44711</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44617</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44496</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44788</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44980</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45288</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>45288</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45007</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>44880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45280</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44838</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44579</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45091</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44991</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>45057</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>45425</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>45392</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44880</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>44931</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45181</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>44508</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>44488</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45201</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44760</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44834</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45730</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44987</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45321</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44872</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45288</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45071</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44676</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>44931</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44596</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44826</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44582</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45075</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>45609</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>45434</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>45384</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>44834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>45253</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>44830</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>44540</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>45646</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>45882</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>45056</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>45628</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>44540</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>44901</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44992</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45726</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>45628</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>45177</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>45128</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>45894</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>44616</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>45628</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>46139</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>44882</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>44936</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45896</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45071</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44659</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>46008</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>44644</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>45072</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>45525</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>45204</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>45006</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45288</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45146</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>45131</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45422</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>45041</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45965</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44963</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>44946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>46077</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>45973</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45979</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>45692</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>45551</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>44936</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>44979</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>46167</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45189</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45986</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44987</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45209</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>45986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>46167</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>45219</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45226</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>45209</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>46171</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>46171</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45525</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45898</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>46171</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>46009</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>46174</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45061</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>44518</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44525</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>44496</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>44581</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>46031</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>44928</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>46030</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45226</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>46031</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>46030</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>46034</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>46034</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>46035</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>46034</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>44671</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>46035</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45077</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>46034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>46034</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>46034</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>46034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>46035</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>46034</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>46037</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>46036</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>46036</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>46036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>46036</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>46041</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>46041</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45980</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>46044</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45511</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46044</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>46035</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45177</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>46043</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45044</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45044</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45237</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>46073</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>46188</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>46075</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>46078</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45219</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>46188</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44579</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>46087</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45957</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>46195</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>46195</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44834</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44953</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44846</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44998</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45235</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>44998</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>46129</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>44987</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>46129</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>46129</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>46129</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45014</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45684</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45152</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>44901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44571</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44617</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45121</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>46212</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>46217</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44900</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45288</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>44953</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45051</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>46272</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45733</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45204</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44496</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>46278</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>46278</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44699</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>44831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44831</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44617</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>44980</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>44931</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45248</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>44881</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>44894</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45128</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45089</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>46288</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>44713</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45016</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45058</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45681</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45681</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44613</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44827</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45401</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>46255</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45817</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>46255</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45001</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44805</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45629</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45799</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45743</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45831</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45799</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45838</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45854</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45491</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45235</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45226</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>45995</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>46027</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>44642</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>44834</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44641</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45988</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>44840</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>44579</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44711</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44530</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>44841</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>46078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44574</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>45896</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>46155</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>45642</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45310</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>46030</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>46160</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44515</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45215</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>44545</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45224</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45911</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45044</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45224</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45904</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45905</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44726</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45531</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44579</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44637</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44495</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44608</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44641</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44641</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44708</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44763</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44519</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44873</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44524</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44711</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44830</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44799</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44872</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44872</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44617</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44706</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44615</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44505</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44711</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44540</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44998</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44496</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44788</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>45044</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45044</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45189</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45072</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44617</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45401</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44571</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44826</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45425</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45006</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>45056</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44760</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>46077</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44894</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45041</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45422</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>46167</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>44987</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>46171</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>46171</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>46171</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45434</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44963</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45384</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44834</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>46174</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45014</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45089</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45061</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>45091</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45392</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>45131</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44872</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44831</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44831</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45075</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>44931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>45058</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>44525</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44644</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>46188</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>46188</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45219</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>45226</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>46195</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>46195</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45181</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45965</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>44980</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44987</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44900</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>44834</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44979</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>44596</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>44846</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44953</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45979</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45986</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45986</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>46212</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>44904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44881</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>46217</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>44880</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45817</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45226</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>45898</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>46278</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>46278</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>46009</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44805</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>46030</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>46030</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>46031</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>46034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>46034</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>46034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>46031</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>46034</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>46034</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>46034</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>46034</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>46034</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>46034</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>46035</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>46036</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>46035</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>46036</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>46036</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>46036</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>46036</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>46035</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>46037</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>44581</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>46041</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>46041</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>45980</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>46044</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>46044</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>46035</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>46288</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>45799</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46043</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45743</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>46075</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>46073</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>46078</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45831</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>46087</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45838</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45799</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>46255</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45681</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>44508</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45957</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46255</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>44928</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45854</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45491</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>46129</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>46129</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46129</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>46129</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45882</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45646</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44671</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45684</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45280</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45628</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44616</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>46272</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45692</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45146</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45628</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44617</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45730</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>46139</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45628</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>44936</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44659</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45209</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45209</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>45235</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45551</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>46008</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44992</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>44946</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44998</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>44931</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44496</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44991</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45057</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44540</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>44713</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45511</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45051</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44953</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45007</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45248</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44931</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44838</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45016</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45077</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45204</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45204</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45733</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44496</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45321</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45071</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>44518</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44901</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45128</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45288</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45121</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44571</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45152</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>44936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>44980</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45177</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45288</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>45288</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45265</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45288</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>44613</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>45071</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45609</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44579</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44579</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>44676</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>44830</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45177</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45253</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45201</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45681</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45681</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45189</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45726</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45525</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45219</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45237</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>44946</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>44987</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44827</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44496</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>45128</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44882</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>44582</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45288</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>44901</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>44834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>44496</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>44699</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>44880</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45525</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>44992</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45235</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45226</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45995</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>46027</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>

--- a/Översikt STRÄNGNÄS.xlsx
+++ b/Översikt STRÄNGNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45505</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45681</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44980</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>44642</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>44834</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44641</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45988</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>44840</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>44579</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44711</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44530</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>44841</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>46078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44574</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>45896</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>46155</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>45642</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45310</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>46030</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>46160</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44515</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45215</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>44545</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45224</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45911</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45044</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45224</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45904</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45905</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44726</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45531</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44874</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44579</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44637</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44495</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44608</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44641</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44641</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44708</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44763</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44519</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44873</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44524</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44711</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>44830</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44799</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44872</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44872</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44617</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44706</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44615</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44505</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44711</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44540</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44998</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44496</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44788</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>45044</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45044</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45189</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45072</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44617</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45401</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44571</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44826</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45425</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45006</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>45056</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44760</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>46077</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44894</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45041</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45422</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>46167</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>44987</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>46171</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>46171</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>46171</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45434</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44963</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45384</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44834</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>46174</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45014</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45089</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45061</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>45091</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45392</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>45131</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44872</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44831</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44831</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45075</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>44931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>45058</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>44525</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44644</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>46188</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>46188</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45219</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>45226</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>46195</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>46195</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45181</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45965</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>44980</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44987</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44900</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>44834</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44979</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>44596</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>44846</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44953</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45979</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45986</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45986</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>46212</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>44904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44881</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>46217</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>44880</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45817</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45226</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>45898</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>46278</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>46278</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>46009</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44805</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>46030</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>46030</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>46031</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>46034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>46034</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>46034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>46031</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>46034</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>46034</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>46034</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>46034</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>46034</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>46034</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>46035</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>46036</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>46035</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>46036</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>46036</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>46036</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>46036</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>46035</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>46037</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>44581</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>46041</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>46041</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>45980</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>46044</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>46044</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>46035</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>46288</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>45799</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46043</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45743</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>46075</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>46073</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>46078</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45831</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>46087</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45838</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45799</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>46255</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45681</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>44508</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45957</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46255</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>44928</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45854</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45491</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>46129</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>46129</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46129</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>46129</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45882</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45646</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44671</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45684</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45280</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45628</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44616</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>46272</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45692</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45146</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45628</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44617</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45730</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>46139</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45628</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>44936</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44659</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45209</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45209</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>45235</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45551</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>46008</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44992</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>44946</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44998</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>44931</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44496</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44991</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45057</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44540</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>44713</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45511</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45051</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44953</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45007</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45248</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44931</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44838</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45016</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45077</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45204</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45204</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45733</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44496</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45321</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45071</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>44518</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44901</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45128</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45288</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45121</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44571</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45152</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>44936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>44980</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45177</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45288</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>45288</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45265</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45288</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>44613</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>45071</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45609</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44579</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44579</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>44676</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>44830</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45177</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45253</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45201</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45681</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45681</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45189</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45726</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45525</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45219</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45237</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>44946</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>44987</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44827</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44496</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>45128</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44882</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>44582</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45288</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>44901</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>44834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>44496</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>44699</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>44880</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45525</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>44992</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45235</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45226</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45995</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>46027</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
